--- a/static/standards-correlations/Virginia_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Virginia_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$29</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | 2024 CS Standards of Learning - the 2017 SOL are superseded</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | 2024 CS Standards of Learning - the 2017 SOL are superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -964,7 +965,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>The collaboration happens; the project-management scaffolding around it does not. Labs are team-based throughout, PreLab 0 establishes a shared working agreement, and Discovery Systems 3 makes the cost of uncoordinated work explicit by forbidding mid-task correction in one round. Peer review appears in Ext 3.3B, where partners exchange libraries and report what made them usable. Twenty reflection prompts across the labs require students to justify a choice or name a trade-off. covers justifying design choices. NOT MET: project management frameworks and methodologies, distributed roles and responsibilities, timelines and project scope, project management tools, and structured reflection on the collaborative experience.</t>
+          <t>The collaboration happens; the project-management scaffolding around it does not. Labs are team-based throughout, PreLab 0 establishes a shared working agreement, and Introductory Systems 3 makes the cost of uncoordinated work explicit by forbidding mid-task correction in one round. Peer review appears in Ext 3.3B, where partners exchange libraries and report what made them usable. Twenty reflection prompts across the labs require students to justify a choice or name a trade-off. covers justifying design choices. NOT MET: project management frameworks and methodologies, distributed roles and responsibilities, timelines and project scope, project management tools, and structured reflection on the collaborative experience.</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1548,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Societal and ethical impacts are core and well evidenced; environmental impact is entirely absent. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app that routes a driver into a wall and Unit 1.4 through a delivery app whose model has drifted. Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a deployed system should exist and Ext 5.3D (Who's Left Out?) asks who it excludes; Discovery Systems 12 asks whose responsibility it is to anticipate harm. NOT MET: the environmental impact of computing in sub-bullets (b) and (c), and quantum computing. Environmental impact is a growing standard nationally and this curriculum has nothing on it.</t>
+          <t>Societal and ethical impacts are core and well evidenced; environmental impact is entirely absent. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app that routes a driver into a wall and Unit 1.4 through a delivery app whose model has drifted. Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a deployed system should exist and Ext 5.3D (Who's Left Out?) asks who it excludes; Introductory Systems 12 asks whose responsibility it is to anticipate harm. NOT MET: the environmental impact of computing in sub-bullets (b) and (c), and quantum computing. Environmental impact is a growing standard nationally and this curriculum has nothing on it.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1610,7 @@
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>NOT ADDRESSED. The history of computing, the contributions of named pioneers, and Moore's Law appear nowhere in either track or in the Discovery projects. There is no adjacent evidence. This would be straightforward to add - a single reading-and-reflection Extension in any unit could carry it - but at present it is a genuine gap.</t>
+          <t>NOT ADDRESSED. The history of computing, the contributions of named pioneers, and Moore's Law appear nowhere in either track or in the Introductory projects. There is no adjacent evidence. This would be straightforward to add - a single reading-and-reflection Extension in any unit could carry it - but at present it is a genuine gap.</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1688,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>Extension-weighted and partial in scope. Ext 5.3F (Talking to a Server) traces a file from the student's own machine across the internet to a remote server and asks what has to go right for that to work - address routing, server uptime, the local connection - which touches the client and server roles and sub-bullet (e). Ext 5.3G (Secret Messages / HTTPS) covers HTTPS by name and why the s matters. Discovery Systems 9 covers senders, receivers, and protocols. NOT MET: routers and switches by name, TCP/IP, network topology diagrams, and modelling communication through the protocol stack. Network hardware is a known recurring gap for this curriculum.</t>
+          <t>Extension-weighted and partial in scope. Ext 5.3F (Talking to a Server) traces a file from the student's own machine across the internet to a remote server and asks what has to go right for that to work - address routing, server uptime, the local connection - which touches the client and server roles and sub-bullet (e). Ext 5.3G (Secret Messages / HTTPS) covers HTTPS by name and why the s matters. Introductory Systems 9 covers senders, receivers, and protocols. NOT MET: routers and switches by name, TCP/IP, network topology diagrams, and modelling communication through the protocol stack. Network hardware is a known recurring gap for this curriculum.</t>
         </is>
       </c>
     </row>
@@ -1721,6 +1722,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1765,7 +1767,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1779,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1901,6 +1903,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
@@ -1926,7 +1930,7 @@
 MANDATE CONTEXT: Virginia does not require a computer science credit for high school graduation. VDOE runs the Advancing Computer Science Education (ACSE) competitive grant program, whose FY27 RFP explicitly funds development of high-quality instructional resources and curriculum aligned to the 2024 CS SOL, plus professional development and career exposure. A Virginia division adopting this curriculum could plausibly fund the gap-filling work identified below through that grant - that is the most useful practical route this file suggests.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 *** RESULT: 6 Full, 14 Partial, 5 blank of 25. Touched 20 of 25. ***
 THIS IS THE WEAKEST STATE FILE IN THE SERIES, AND THAT IS AN HONEST RESULT. Do not present Virginia as a strong alignment. The reason is structural and worth stating plainly to a division:
